--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_149_R15.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_149_R15.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.4086</v>
+        <v>6.3193</v>
       </c>
       <c r="E2" t="n">
-        <v>6.5587</v>
+        <v>5.8391</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8499</v>
+        <v>0.4802</v>
       </c>
       <c r="G2" t="n">
         <v>2.109</v>
@@ -610,13 +610,13 @@
         <v>2.3195</v>
       </c>
       <c r="S2" t="n">
-        <v>2.1398</v>
+        <v>1.0506</v>
       </c>
       <c r="T2" t="n">
-        <v>1.6201</v>
+        <v>0.9006</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5197000000000001</v>
+        <v>0.15</v>
       </c>
       <c r="V2" t="n">
         <v>1.0722</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.9939</v>
+        <v>3.7862</v>
       </c>
       <c r="E3" t="n">
-        <v>4.7893</v>
+        <v>3.2874</v>
       </c>
       <c r="F3" t="n">
-        <v>1.2046</v>
+        <v>0.4988</v>
       </c>
       <c r="G3" t="n">
         <v>0.7694</v>
@@ -688,13 +688,13 @@
         <v>2.0876</v>
       </c>
       <c r="S3" t="n">
-        <v>3.3664</v>
+        <v>1.1587</v>
       </c>
       <c r="T3" t="n">
-        <v>2.4065</v>
+        <v>0.9045</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9599</v>
+        <v>0.2541</v>
       </c>
       <c r="V3" t="n">
         <v>0.9304</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5292</v>
+        <v>3.5537</v>
       </c>
       <c r="E4" t="n">
-        <v>2.7424</v>
+        <v>3.3636</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2132</v>
+        <v>0.1901</v>
       </c>
       <c r="G4" t="n">
         <v>-0.8250999999999999</v>
@@ -766,13 +766,13 @@
         <v>1.8556</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.1817</v>
+        <v>-0.1573</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7389</v>
+        <v>-0.1177</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4428</v>
+        <v>-0.0395</v>
       </c>
       <c r="V4" t="n">
         <v>2.6805</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>B. FERNANDO</t>
+          <t>V. MARINKOVIC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3269</v>
+        <v>0.5036</v>
       </c>
       <c r="E5" t="n">
-        <v>1.5684</v>
+        <v>-1.2651</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.2415</v>
+        <v>1.7686</v>
       </c>
       <c r="G5" t="n">
-        <v>1.749</v>
+        <v>-1.5886</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.4227</v>
+        <v>-0.0862</v>
       </c>
       <c r="I5" t="n">
-        <v>2.1716</v>
+        <v>-1.5023</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9663</v>
+        <v>-2.1174</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.2115</v>
+        <v>0.168</v>
       </c>
       <c r="L5" t="n">
-        <v>1.1778</v>
+        <v>-2.2854</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7827</v>
+        <v>0.5288</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2112</v>
+        <v>-0.2543</v>
       </c>
       <c r="O5" t="n">
-        <v>0.9939</v>
+        <v>0.7831</v>
       </c>
       <c r="P5" t="n">
+        <v>1.3917</v>
+      </c>
+      <c r="Q5" t="n">
         <v>-0.232</v>
       </c>
-      <c r="Q5" t="n">
-        <v>-1.1598</v>
-      </c>
       <c r="R5" t="n">
-        <v>0.9278</v>
+        <v>1.6237</v>
       </c>
       <c r="S5" t="n">
-        <v>1.8125</v>
+        <v>-0.23</v>
       </c>
       <c r="T5" t="n">
-        <v>1.6201</v>
+        <v>0.0121</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1924</v>
+        <v>-0.242</v>
       </c>
       <c r="V5" t="n">
-        <v>-2.0026</v>
+        <v>0.9304</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1418</v>
+        <v>1.0722</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.1444</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>V. MARINKOVIC</t>
+          <t>S. MILTON</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.464</v>
+        <v>0.0059</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.1654</v>
+        <v>-3.5116</v>
       </c>
       <c r="F6" t="n">
-        <v>1.7014</v>
+        <v>3.5176</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.5886</v>
+        <v>0.021</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.0862</v>
+        <v>0.1246</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.5023</v>
+        <v>-0.1036</v>
       </c>
       <c r="J6" t="n">
-        <v>-2.1174</v>
+        <v>-0.7796</v>
       </c>
       <c r="K6" t="n">
-        <v>0.168</v>
+        <v>0.6827</v>
       </c>
       <c r="L6" t="n">
-        <v>-2.2854</v>
+        <v>-1.4623</v>
       </c>
       <c r="M6" t="n">
-        <v>0.5288</v>
+        <v>0.8006</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2543</v>
+        <v>-0.5581</v>
       </c>
       <c r="O6" t="n">
-        <v>0.7831</v>
+        <v>1.3586</v>
       </c>
       <c r="P6" t="n">
-        <v>1.3917</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.232</v>
+        <v>-2.5515</v>
       </c>
       <c r="R6" t="n">
-        <v>1.6237</v>
+        <v>2.5515</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.1975</v>
+        <v>0.1267</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8883</v>
+        <v>-0.1806</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3093</v>
+        <v>0.3073</v>
       </c>
       <c r="V6" t="n">
-        <v>0.9304</v>
+        <v>-0.1418</v>
       </c>
       <c r="W6" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>-0.1418</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. MILTON</t>
+          <t>B. FERNANDO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.8101</v>
+        <v>-0.0885</v>
       </c>
       <c r="E7" t="n">
-        <v>-4.294</v>
+        <v>0.153</v>
       </c>
       <c r="F7" t="n">
-        <v>3.484</v>
+        <v>-0.2415</v>
       </c>
       <c r="G7" t="n">
-        <v>0.021</v>
+        <v>1.749</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1246</v>
+        <v>-0.4227</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1036</v>
+        <v>2.1716</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.7796</v>
+        <v>0.9663</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6827</v>
+        <v>-0.2115</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.4623</v>
+        <v>1.1778</v>
       </c>
       <c r="M7" t="n">
-        <v>0.8006</v>
+        <v>0.7827</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5581</v>
+        <v>-0.2112</v>
       </c>
       <c r="O7" t="n">
-        <v>1.3586</v>
+        <v>0.9939</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-0.232</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.5515</v>
+        <v>-1.1598</v>
       </c>
       <c r="R7" t="n">
-        <v>2.5515</v>
+        <v>0.9278</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6893</v>
+        <v>0.3971</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.963</v>
+        <v>0.2047</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2737</v>
+        <v>0.1924</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.1418</v>
+        <v>-2.0026</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1418</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. OSETKOWSKI</t>
+          <t>S. BROWN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.3004</v>
+        <v>-0.8777</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.2834</v>
+        <v>-2.8857</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.017</v>
+        <v>2.008</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.5104</v>
+        <v>-1.5894</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1452</v>
+        <v>0.0634</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.3652</v>
+        <v>-1.6528</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.7527</v>
+        <v>-1.2323</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0336</v>
+        <v>0.4642</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.7863</v>
+        <v>-1.6965</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.7577</v>
+        <v>-0.3571</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1788</v>
+        <v>-0.4008</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.5788</v>
+        <v>0.0437</v>
       </c>
       <c r="P8" t="n">
-        <v>0.4639</v>
+        <v>-0.232</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.232</v>
+        <v>-2.5515</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6959</v>
+        <v>2.3195</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2539</v>
+        <v>0.5493</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2987</v>
+        <v>0.362</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0448</v>
+        <v>0.1874</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.3943</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.5361</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S. BROWN</t>
+          <t>D. OSETKOWSKI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.0715</v>
+        <v>-1.0406</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.9787</v>
+        <v>-1.0908</v>
       </c>
       <c r="F9" t="n">
-        <v>1.9072</v>
+        <v>0.0502</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.5894</v>
+        <v>-1.5104</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0634</v>
+        <v>-0.1452</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.6528</v>
+        <v>-1.3652</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.2323</v>
+        <v>-0.7527</v>
       </c>
       <c r="K9" t="n">
-        <v>0.4642</v>
+        <v>0.0336</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.6965</v>
+        <v>-0.7863</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.3571</v>
+        <v>-0.7577</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.4008</v>
+        <v>-0.1788</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0437</v>
+        <v>-0.5788</v>
       </c>
       <c r="P9" t="n">
+        <v>0.4639</v>
+      </c>
+      <c r="Q9" t="n">
         <v>-0.232</v>
       </c>
-      <c r="Q9" t="n">
-        <v>-2.5515</v>
-      </c>
       <c r="R9" t="n">
-        <v>2.3195</v>
+        <v>0.6959</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6445</v>
+        <v>0.0059</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.731</v>
+        <v>-0.1061</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0866</v>
+        <v>0.112</v>
       </c>
       <c r="V9" t="n">
-        <v>0.3943</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.4383</v>
+        <v>-1.782</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.9002</v>
+        <v>-2.5463</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4619</v>
+        <v>0.7643</v>
       </c>
       <c r="G10" t="n">
         <v>-0.8827</v>
@@ -1234,13 +1234,13 @@
         <v>0.4639</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8597</v>
+        <v>-0.2034</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5895</v>
+        <v>-0.2357</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2702</v>
+        <v>0.0323</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-7.5429</v>
+        <v>-6.6283</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.328</v>
+        <v>-5.5142</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.2149</v>
+        <v>-1.1141</v>
       </c>
       <c r="G11" t="n">
         <v>-1.891</v>
@@ -1312,13 +1312,13 @@
         <v>1.3917</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.3324</v>
+        <v>-0.4178</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.963</v>
+        <v>-0.1491</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3694</v>
+        <v>-0.2686</v>
       </c>
       <c r="V11" t="n">
         <v>-1.0722</v>
@@ -1345,16 +1345,16 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>2.6314</v>
+        <v>3.751599999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.2909</v>
+        <v>-4.1706</v>
       </c>
       <c r="F12" t="n">
-        <v>7.9224</v>
+        <v>7.9222</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.638800000000001</v>
+        <v>-3.6388</v>
       </c>
       <c r="H12" t="n">
         <v>5.3111</v>
@@ -1363,7 +1363,7 @@
         <v>-8.949999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>0.8991000000000005</v>
+        <v>0.8991000000000009</v>
       </c>
       <c r="K12" t="n">
         <v>9.265000000000001</v>
@@ -1381,7 +1381,7 @@
         <v>-0.5839999999999999</v>
       </c>
       <c r="P12" t="n">
-        <v>2.3194</v>
+        <v>2.319400000000001</v>
       </c>
       <c r="Q12" t="n">
         <v>-13.9174</v>
@@ -1390,10 +1390,10 @@
         <v>16.2367</v>
       </c>
       <c r="S12" t="n">
-        <v>1.159699999999999</v>
+        <v>2.2798</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4742999999999996</v>
+        <v>1.5947</v>
       </c>
       <c r="U12" t="n">
         <v>0.6854</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.6368</v>
+        <v>3.5125</v>
       </c>
       <c r="E13" t="n">
-        <v>2.623</v>
+        <v>1.9153</v>
       </c>
       <c r="F13" t="n">
-        <v>1.0139</v>
+        <v>1.5973</v>
       </c>
       <c r="G13" t="n">
         <v>1.1039</v>
@@ -1468,13 +1468,13 @@
         <v>1.6237</v>
       </c>
       <c r="S13" t="n">
-        <v>0.2109</v>
+        <v>0.08649999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>1.0069</v>
+        <v>0.2992</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.796</v>
+        <v>-0.2126</v>
       </c>
       <c r="V13" t="n">
         <v>0.9304</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.322</v>
+        <v>1.6923</v>
       </c>
       <c r="E14" t="n">
-        <v>1.4128</v>
+        <v>1.6487</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.09080000000000001</v>
+        <v>0.0436</v>
       </c>
       <c r="G14" t="n">
         <v>1.0184</v>
@@ -1546,13 +1546,13 @@
         <v>1.6237</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.8381999999999999</v>
+        <v>-0.4679</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.7468</v>
+        <v>-0.5109</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0914</v>
+        <v>0.0431</v>
       </c>
       <c r="V14" t="n">
         <v>0.6778999999999999</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5933</v>
+        <v>0.8591</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.6506</v>
+        <v>-1.0608</v>
       </c>
       <c r="F15" t="n">
-        <v>2.2439</v>
+        <v>1.9199</v>
       </c>
       <c r="G15" t="n">
         <v>4.3167</v>
@@ -1624,13 +1624,13 @@
         <v>2.3195</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3317</v>
+        <v>-0.0659</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.0965</v>
+        <v>-0.5067</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7648</v>
+        <v>0.4408</v>
       </c>
       <c r="V15" t="n">
         <v>-1.0722</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. DAVIDOVAC</t>
+          <t>N. KALINIC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0184</v>
+        <v>0.0612</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.7517</v>
+        <v>-1.3869</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7701</v>
+        <v>1.4481</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.4782</v>
+        <v>0.5927</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.0768</v>
+        <v>-0.8964</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4015</v>
+        <v>1.489</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.8738</v>
+        <v>0.9476</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.1611</v>
+        <v>0.9243</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.7127</v>
+        <v>0.0234</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.6044</v>
+        <v>-0.355</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.9157</v>
+        <v>-1.8206</v>
       </c>
       <c r="O16" t="n">
-        <v>0.3113</v>
+        <v>1.4657</v>
       </c>
       <c r="P16" t="n">
-        <v>1.1598</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-2.5515</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1598</v>
+        <v>1.8556</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3369</v>
+        <v>0.0226</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1221</v>
+        <v>0.0751</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2148</v>
+        <v>-0.0525</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>N. KALINIC</t>
+          <t>J. BUTLER</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.3212</v>
+        <v>-0.1468</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.6228</v>
+        <v>-0.8378</v>
       </c>
       <c r="F17" t="n">
-        <v>1.3016</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5927</v>
+        <v>1.1648</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.8964</v>
+        <v>0.7334000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>1.489</v>
+        <v>0.4314</v>
       </c>
       <c r="J17" t="n">
-        <v>0.9476</v>
+        <v>1.1189</v>
       </c>
       <c r="K17" t="n">
-        <v>0.9243</v>
+        <v>1.8387</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0234</v>
+        <v>-0.7198</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.355</v>
+        <v>0.0458</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.8206</v>
+        <v>-1.1053</v>
       </c>
       <c r="O17" t="n">
-        <v>1.4657</v>
+        <v>1.1511</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.6959</v>
+        <v>-1.3917</v>
       </c>
       <c r="Q17" t="n">
         <v>-2.5515</v>
       </c>
       <c r="R17" t="n">
-        <v>1.8556</v>
+        <v>1.1598</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3598</v>
+        <v>-0.2034</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1608</v>
+        <v>0.1693</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.199</v>
+        <v>-0.3727</v>
       </c>
       <c r="V17" t="n">
-        <v>0.1418</v>
+        <v>0.2836</v>
       </c>
       <c r="W17" t="n">
-        <v>0.1418</v>
+        <v>0.4254</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>E. IZUNDU</t>
+          <t>D. DAVIDOVAC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4029</v>
+        <v>-0.1839</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6011</v>
+        <v>-0.9876</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.004</v>
+        <v>0.8037</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.6637</v>
+        <v>-1.4782</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.2125</v>
+        <v>-1.0768</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5488</v>
+        <v>-0.4015</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.8173</v>
+        <v>-0.8738</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.0013</v>
+        <v>-0.1611</v>
       </c>
       <c r="L18" t="n">
-        <v>0.184</v>
+        <v>-0.7127</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1536</v>
+        <v>-0.6044</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2112</v>
+        <v>-0.9157</v>
       </c>
       <c r="O18" t="n">
-        <v>0.3648</v>
+        <v>0.3113</v>
       </c>
       <c r="P18" t="n">
-        <v>0.6959</v>
+        <v>1.1598</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.232</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9278</v>
+        <v>1.1598</v>
       </c>
       <c r="S18" t="n">
-        <v>0.7789</v>
+        <v>0.1346</v>
       </c>
       <c r="T18" t="n">
-        <v>0.5780999999999999</v>
+        <v>-0.1138</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2008</v>
+        <v>0.2484</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.214</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.2862</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. BUTLER</t>
+          <t>E. IZUNDU</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.5114</v>
+        <v>-0.4987</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.7199</v>
+        <v>0.2472</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2085</v>
+        <v>-0.7459</v>
       </c>
       <c r="G19" t="n">
-        <v>1.1648</v>
+        <v>-0.6637</v>
       </c>
       <c r="H19" t="n">
-        <v>0.7334000000000001</v>
+        <v>-1.2125</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4314</v>
+        <v>0.5488</v>
       </c>
       <c r="J19" t="n">
-        <v>1.1189</v>
+        <v>-0.8173</v>
       </c>
       <c r="K19" t="n">
-        <v>1.8387</v>
+        <v>-1.0013</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.7198</v>
+        <v>0.184</v>
       </c>
       <c r="M19" t="n">
-        <v>0.0458</v>
+        <v>0.1536</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.1053</v>
+        <v>-0.2112</v>
       </c>
       <c r="O19" t="n">
-        <v>1.1511</v>
+        <v>0.3648</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.3917</v>
+        <v>0.6959</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.5515</v>
+        <v>-0.232</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1598</v>
+        <v>0.9278</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5679999999999999</v>
+        <v>0.6831</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2873</v>
+        <v>0.2243</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.8552999999999999</v>
+        <v>0.4589</v>
       </c>
       <c r="V19" t="n">
-        <v>0.2836</v>
+        <v>-1.214</v>
       </c>
       <c r="W19" t="n">
-        <v>0.4254</v>
+        <v>1.0722</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.1418</v>
+        <v>-2.2862</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.5998</v>
+        <v>-1.3924</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0201</v>
+        <v>-0.0978</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.6199</v>
+        <v>-1.2946</v>
       </c>
       <c r="G20" t="n">
         <v>-0.6503</v>
@@ -2014,13 +2014,13 @@
         <v>0.6959</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1788</v>
+        <v>0.0286</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4208</v>
+        <v>0.3029</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5996</v>
+        <v>-0.2743</v>
       </c>
       <c r="V20" t="n">
         <v>-1.4665</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.3667</v>
+        <v>-4.9621</v>
       </c>
       <c r="E21" t="n">
-        <v>-7.6925</v>
+        <v>-7.2206</v>
       </c>
       <c r="F21" t="n">
-        <v>2.3257</v>
+        <v>2.2585</v>
       </c>
       <c r="G21" t="n">
         <v>-1.765</v>
@@ -2092,13 +2092,13 @@
         <v>2.5515</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.21</v>
+        <v>0.1946</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.0965</v>
+        <v>-0.6247</v>
       </c>
       <c r="U21" t="n">
-        <v>0.8865</v>
+        <v>0.8193</v>
       </c>
       <c r="V21" t="n">
         <v>-1.0722</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.6315</v>
+        <v>-1.0588</v>
       </c>
       <c r="E22" t="n">
-        <v>-7.7805</v>
+        <v>-7.7803</v>
       </c>
       <c r="F22" t="n">
-        <v>5.149</v>
+        <v>6.7216</v>
       </c>
       <c r="G22" t="n">
         <v>3.6393</v>
@@ -2146,10 +2146,10 @@
         <v>4.538</v>
       </c>
       <c r="K22" t="n">
-        <v>3.954000000000001</v>
+        <v>3.954</v>
       </c>
       <c r="L22" t="n">
-        <v>0.5841999999999997</v>
+        <v>0.5841999999999999</v>
       </c>
       <c r="M22" t="n">
         <v>-0.8989000000000001</v>
@@ -2170,13 +2170,13 @@
         <v>13.9173</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.1598</v>
+        <v>0.4128000000000001</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6854000000000002</v>
+        <v>-0.6853</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4744</v>
+        <v>1.0984</v>
       </c>
       <c r="V22" t="n">
         <v>-2.7912</v>
